--- a/data/s3/Aradas/archetypes/pop_archetypes_citizen.xlsx
+++ b/data/s3/Aradas/archetypes/pop_archetypes_citizen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\s3\Aradas\archetypes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asier.divasson\Documents\GitHub\CogniCity\data\Aradas\archetypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EC366E-12EC-4D86-A28A-A952A8DE5A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1BEF6D-93C8-4E84-B2E3-F8176908639A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -217,7 +217,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,12 +242,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -261,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -274,7 +268,6 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,10 +672,10 @@
       <c r="AD1" t="s">
         <v>34</v>
       </c>
-      <c r="AE1" s="12" t="s">
+      <c r="AE1" t="s">
         <v>35</v>
       </c>
-      <c r="AF1" s="12" t="s">
+      <c r="AF1" t="s">
         <v>36</v>
       </c>
       <c r="AG1" t="s">
@@ -691,10 +684,10 @@
       <c r="AH1" t="s">
         <v>46</v>
       </c>
-      <c r="AI1" s="12" t="s">
+      <c r="AI1" t="s">
         <v>37</v>
       </c>
-      <c r="AJ1" s="12" t="s">
+      <c r="AJ1" t="s">
         <v>38</v>
       </c>
       <c r="AK1" t="s">
@@ -796,13 +789,11 @@
       <c r="AD2" s="10">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="AE2" s="12">
-        <f>1215*0.935</f>
-        <v>1136.0250000000001</v>
-      </c>
-      <c r="AF2" s="12">
-        <f>1156.6*0.935</f>
-        <v>1081.421</v>
+      <c r="AE2" s="7">
+        <v>1215</v>
+      </c>
+      <c r="AF2" s="7">
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG2" s="7">
         <v>0</v>
@@ -810,13 +801,11 @@
       <c r="AH2" s="7">
         <v>99999</v>
       </c>
-      <c r="AI2" s="12">
-        <f>1872*0.935</f>
-        <v>1750.3200000000002</v>
-      </c>
-      <c r="AJ2" s="12">
-        <f>1182*0.935</f>
-        <v>1105.17</v>
+      <c r="AI2" s="7">
+        <v>1872</v>
+      </c>
+      <c r="AJ2" s="7">
+        <v>1182</v>
       </c>
       <c r="AK2" s="7">
         <v>0</v>
@@ -917,13 +906,11 @@
       <c r="AD3" s="10">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="AE3" s="12">
-        <f>1215*0.935</f>
-        <v>1136.0250000000001</v>
-      </c>
-      <c r="AF3" s="12">
-        <f>1156.6*0.935</f>
-        <v>1081.421</v>
+      <c r="AE3" s="7">
+        <v>1215</v>
+      </c>
+      <c r="AF3" s="7">
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG3" s="7">
         <v>0</v>
@@ -931,13 +918,11 @@
       <c r="AH3" s="7">
         <v>99999</v>
       </c>
-      <c r="AI3" s="12">
-        <f>1872*0.935</f>
-        <v>1750.3200000000002</v>
-      </c>
-      <c r="AJ3" s="12">
-        <f>1182*0.935</f>
-        <v>1105.17</v>
+      <c r="AI3" s="7">
+        <v>1872</v>
+      </c>
+      <c r="AJ3" s="7">
+        <v>1182</v>
       </c>
       <c r="AK3" s="7">
         <v>0</v>
@@ -1037,13 +1022,11 @@
       <c r="AD4" s="10">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="AE4" s="12">
-        <f>2708*0.935</f>
-        <v>2531.98</v>
-      </c>
-      <c r="AF4" s="12">
-        <f>1156.6*0.935</f>
-        <v>1081.421</v>
+      <c r="AE4" s="7">
+        <v>2708</v>
+      </c>
+      <c r="AF4" s="7">
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG4" s="7">
         <v>0</v>
@@ -1051,13 +1034,11 @@
       <c r="AH4" s="7">
         <v>99999</v>
       </c>
-      <c r="AI4" s="12">
-        <f>1872*0.935</f>
-        <v>1750.3200000000002</v>
-      </c>
-      <c r="AJ4" s="12">
-        <f>1182*0.935</f>
-        <v>1105.17</v>
+      <c r="AI4" s="7">
+        <v>1872</v>
+      </c>
+      <c r="AJ4" s="7">
+        <v>1182</v>
       </c>
       <c r="AK4" s="7">
         <v>0</v>
@@ -1116,7 +1097,6 @@
         <v>240</v>
       </c>
       <c r="Q5" s="8">
-        <f>1-0.0670582476749878</f>
         <v>0.9329417523250122</v>
       </c>
       <c r="R5" s="11">
@@ -1158,13 +1138,11 @@
       <c r="AD5" s="10">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="AE5" s="12">
-        <f>1215*0.935</f>
-        <v>1136.0250000000001</v>
-      </c>
-      <c r="AF5" s="12">
-        <f>1156.6*0.935</f>
-        <v>1081.421</v>
+      <c r="AE5" s="7">
+        <v>1215</v>
+      </c>
+      <c r="AF5" s="7">
+        <v>1156.5999999999999</v>
       </c>
       <c r="AG5" s="7">
         <v>0</v>
@@ -1172,13 +1150,11 @@
       <c r="AH5" s="7">
         <v>99999</v>
       </c>
-      <c r="AI5" s="12">
-        <f>1872*0.935</f>
-        <v>1750.3200000000002</v>
-      </c>
-      <c r="AJ5" s="12">
-        <f>1182*0.935</f>
-        <v>1105.17</v>
+      <c r="AI5" s="7">
+        <v>1872</v>
+      </c>
+      <c r="AJ5" s="7">
+        <v>1182</v>
       </c>
       <c r="AK5" s="7">
         <v>0</v>
@@ -1278,13 +1254,11 @@
       <c r="AD6" s="10">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="AE6" s="12">
-        <f>1253*0.935</f>
-        <v>1171.5550000000001</v>
-      </c>
-      <c r="AF6" s="12">
-        <f>1155*0.935</f>
-        <v>1079.925</v>
+      <c r="AE6" s="7">
+        <v>1253</v>
+      </c>
+      <c r="AF6" s="7">
+        <v>1155</v>
       </c>
       <c r="AG6" s="7">
         <v>0</v>
@@ -1292,13 +1266,11 @@
       <c r="AH6" s="7">
         <v>99999</v>
       </c>
-      <c r="AI6" s="12">
-        <f>1872*0.935</f>
-        <v>1750.3200000000002</v>
-      </c>
-      <c r="AJ6" s="12">
-        <f>1182*0.935</f>
-        <v>1105.17</v>
+      <c r="AI6" s="7">
+        <v>1872</v>
+      </c>
+      <c r="AJ6" s="7">
+        <v>1182</v>
       </c>
       <c r="AK6" s="7">
         <v>0</v>
@@ -1306,12 +1278,6 @@
       <c r="AL6" s="7">
         <v>99999</v>
       </c>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="Q9" s="3"/>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="Q10" s="3"/>
@@ -1351,6 +1317,7 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="Q14" s="3"/>
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
@@ -1361,6 +1328,7 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="Q15" s="3"/>
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
